--- a/outputs/32337.xlsx
+++ b/outputs/32337.xlsx
@@ -261,8 +261,8 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -664,8 +664,8 @@
         <v>7</v>
       </c>
       <c r="P3" s="15" t="n">
-        <f aca="false">ROUND(($B$1-C3)/365,0)</f>
-        <v>7</v>
+        <f aca="false">(B$1-C3)/365</f>
+        <v>6.87397260273973</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -709,8 +709,8 @@
         <v>6</v>
       </c>
       <c r="P4" s="15" t="n">
-        <f aca="false">ROUND(($B$1-C4)/365,0)</f>
-        <v>6</v>
+        <f aca="false">(B$1-C4)/365</f>
+        <v>6.18904109589041</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -754,8 +754,8 @@
         <v>8</v>
       </c>
       <c r="P5" s="15" t="n">
-        <f aca="false">ROUND(($B$1-C5)/365,0)</f>
-        <v>8</v>
+        <f aca="false">(B$1-C5)/365</f>
+        <v>8.08767123287671</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -799,8 +799,8 @@
         <v>8</v>
       </c>
       <c r="P6" s="15" t="n">
-        <f aca="false">ROUND(($B$1-C6)/365,0)</f>
-        <v>8</v>
+        <f aca="false">(B$1-C6)/365</f>
+        <v>8.22191780821918</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -844,8 +844,8 @@
         <v>8</v>
       </c>
       <c r="P7" s="15" t="n">
-        <f aca="false">ROUND(($B$1-C7)/365,0)</f>
-        <v>8</v>
+        <f aca="false">(B$1-C7)/365</f>
+        <v>7.7013698630137</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -889,8 +889,8 @@
         <v>9</v>
       </c>
       <c r="P8" s="15" t="n">
-        <f aca="false">ROUND(($B$1-C8)/365,0)</f>
-        <v>9</v>
+        <f aca="false">(B$1-C8)/365</f>
+        <v>9.44657534246575</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -934,8 +934,8 @@
         <v>9</v>
       </c>
       <c r="P9" s="15" t="n">
-        <f aca="false">ROUND(($B$1-C9)/365,0)</f>
-        <v>9</v>
+        <f aca="false">(B$1-C9)/365</f>
+        <v>9.18082191780822</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -979,8 +979,8 @@
         <v>9</v>
       </c>
       <c r="P10" s="15" t="n">
-        <f aca="false">ROUND(($B$1-C10)/365,0)</f>
-        <v>9</v>
+        <f aca="false">(B$1-C10)/365</f>
+        <v>9.34246575342466</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1024,8 +1024,8 @@
         <v>8</v>
       </c>
       <c r="P11" s="15" t="n">
-        <f aca="false">ROUND(($B$1-C11)/365,0)</f>
-        <v>8</v>
+        <f aca="false">(B$1-C11)/365</f>
+        <v>7.64931506849315</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1065,8 +1065,8 @@
         <v>10</v>
       </c>
       <c r="P12" s="15" t="n">
-        <f aca="false">ROUND(($B$1-C12)/365,0)</f>
-        <v>10</v>
+        <f aca="false">(B$1-C12)/365</f>
+        <v>10.1150684931507</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1106,8 +1106,8 @@
         <v>10</v>
       </c>
       <c r="P13" s="15" t="n">
-        <f aca="false">ROUND(($B$1-C13)/365,0)</f>
-        <v>10</v>
+        <f aca="false">(B$1-C13)/365</f>
+        <v>9.94520547945206</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1147,8 +1147,8 @@
         <v>10</v>
       </c>
       <c r="P14" s="15" t="n">
-        <f aca="false">ROUND(($B$1-C14)/365,0)</f>
-        <v>10</v>
+        <f aca="false">(B$1-C14)/365</f>
+        <v>9.52328767123288</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1188,8 +1188,8 @@
         <v>12</v>
       </c>
       <c r="P15" s="15" t="n">
-        <f aca="false">ROUND(($B$1-C15)/365,0)</f>
-        <v>12</v>
+        <f aca="false">(B$1-C15)/365</f>
+        <v>11.6027397260274</v>
       </c>
     </row>
   </sheetData>
